--- a/docs/downloads/11/tbl_cata_type_marovoay_madiromiongana.xlsx
+++ b/docs/downloads/11/tbl_cata_type_marovoay_madiromiongana.xlsx
@@ -531,12 +531,6 @@
           <t>Grêle</t>
         </is>
       </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -549,12 +543,6 @@
           <t>Incendie / Foudre</t>
         </is>
       </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -567,12 +555,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -747,12 +729,6 @@
           <t>Grêle</t>
         </is>
       </c>
-      <c r="C22">
-        <v>3</v>
-      </c>
-      <c r="D22">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -764,12 +740,6 @@
         <is>
           <t>Incendie / Foudre</t>
         </is>
-      </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-      <c r="D23">
-        <v>0.4</v>
       </c>
     </row>
   </sheetData>
